--- a/app_proto.xlsx
+++ b/app_proto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\esp32\esp32_common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB4F7D1-2851-4326-BA7F-89FAC56B3250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE11F5EB-0EC6-4DDD-AF55-438A3C35748F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{F18B4279-3DD4-4A7B-B6C0-9AE4AF60F1CA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
   <si>
     <t>ver</t>
   </si>
@@ -257,12 +257,17 @@
     <t>offset</t>
   </si>
   <si>
-    <t>operation
-OP_DOWNLOAD
+    <t>OP_DOWNLOAD
 OP_UPLOAD</t>
   </si>
   <si>
-    <t>OP_UPDATEKEY</t>
+    <t>OP_CONFIG</t>
+  </si>
+  <si>
+    <t>max chunk size</t>
+  </si>
+  <si>
+    <t>max blob size</t>
   </si>
 </sst>
 </file>
@@ -701,7 +706,8 @@
     <col min="6" max="6" width="23.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="53.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="56.42578125" style="8" bestFit="1" customWidth="1"/>
   </cols>
@@ -1206,7 +1212,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -1216,14 +1222,12 @@
         <v>73</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="J22" s="1"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
@@ -1285,12 +1289,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="F20:F22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="B20:B22"/>
     <mergeCell ref="C20:C22"/>
-    <mergeCell ref="B20:B22"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
